--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F8650A-897E-4D1C-A887-347BC21A5BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3685FB-2D2A-4527-986C-2DE440732FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="3" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -1284,32 +1284,32 @@
         <v>13</v>
       </c>
       <c r="C8" s="11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D8" s="11">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E8" s="11">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F8" s="11">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G8" s="11">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H8" s="11">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="I8" s="11">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>9.8000000000000007</v>
+        <v>11.25</v>
       </c>
       <c r="K8" s="12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
@@ -1317,28 +1317,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>30</v>
+      </c>
+      <c r="R8" s="11">
+        <v>50</v>
+      </c>
+      <c r="S8" s="11">
+        <v>30</v>
+      </c>
+      <c r="T8" s="11">
+        <v>30</v>
+      </c>
+      <c r="U8" s="11">
+        <v>30</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="W8" s="12">
+        <v>5</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>9.8000000000000007</v>
+        <v>11.25</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>9.8000000000000007</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -1378,28 +1392,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>79</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>41</v>
+      </c>
+      <c r="S9" s="11">
+        <v>39</v>
+      </c>
+      <c r="T9" s="11">
+        <v>40</v>
+      </c>
+      <c r="U9" s="11">
+        <v>40</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>5.9749999999999996</v>
+      </c>
+      <c r="W9" s="12">
+        <v>23</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>6.0750000000000002</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>5.9749999999999996</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>6.0750000000000002</v>
+        <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -1407,42 +1435,68 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>138</v>
+      </c>
+      <c r="D10" s="11">
+        <v>18</v>
+      </c>
+      <c r="E10" s="11">
+        <v>18</v>
+      </c>
+      <c r="F10" s="11">
+        <v>22</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K10" s="12">
+        <v>6</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
+      <c r="O10" s="11">
+        <v>138</v>
+      </c>
+      <c r="P10" s="11">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>18</v>
+      </c>
+      <c r="R10" s="11">
+        <v>22</v>
+      </c>
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
@@ -1487,29 +1541,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>6</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>12</v>
+      </c>
+      <c r="T11" s="11">
+        <v>6</v>
+      </c>
+      <c r="U11" s="11">
+        <v>12</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>0.9</v>
+      </c>
+      <c r="W11" s="12">
+        <v>2</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>4.9000000000000004</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>4.9000000000000004</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -1550,29 +1620,45 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>176</v>
+      </c>
+      <c r="P12" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>40</v>
+      </c>
+      <c r="R12" s="11">
+        <v>40</v>
+      </c>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>0</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>7.4</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>7.9</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -1612,17 +1698,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>800</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>800</v>
+      </c>
+      <c r="R13" s="11">
+        <v>920</v>
+      </c>
+      <c r="S13" s="11">
+        <v>840</v>
+      </c>
+      <c r="T13" s="11">
+        <v>800</v>
+      </c>
+      <c r="U13" s="11">
+        <v>800</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>124</v>
+      </c>
+      <c r="W13" s="12">
+        <v>2</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -1640,10 +1740,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="K14" s="12">
+        <v>18</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -1783,83 +1884,83 @@
       <c r="B18" s="7"/>
       <c r="C18" s="24">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>302</v>
+        <v>450</v>
       </c>
       <c r="D18" s="24">
         <f t="shared" si="5"/>
-        <v>982</v>
+        <v>1030</v>
       </c>
       <c r="E18" s="24">
         <f t="shared" si="5"/>
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="F18" s="24">
         <f t="shared" si="5"/>
-        <v>1121</v>
+        <v>1113</v>
       </c>
       <c r="G18" s="24">
         <f t="shared" si="5"/>
-        <v>1070</v>
+        <v>1020</v>
       </c>
       <c r="H18" s="24">
         <f t="shared" si="5"/>
-        <v>918</v>
+        <v>976</v>
       </c>
       <c r="I18" s="24">
         <f t="shared" si="5"/>
-        <v>946</v>
+        <v>996</v>
       </c>
       <c r="J18" s="19">
         <f>SUM(C18:I18)</f>
-        <v>6307</v>
+        <v>6561</v>
       </c>
       <c r="K18" s="27"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="24">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="P18" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="Q18" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="R18" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="S18" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="T18" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="U18" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="V18" s="19">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>5927</v>
       </c>
       <c r="W18" s="27"/>
       <c r="Y18" s="31">
         <f>SUM(Y8:Y17)</f>
-        <v>28.674999999999997</v>
+        <v>35.024999999999999</v>
       </c>
       <c r="Z18" s="32">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>24.174999999999997</v>
       </c>
       <c r="AA18" s="42">
         <f>SUM(AA8:AA17)</f>
-        <v>28.674999999999997</v>
+        <v>10.850000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1869,35 +1970,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>7.55</v>
+        <v>11.25</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>24.55</v>
+        <v>25.75</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>28.024999999999999</v>
+        <v>27.824999999999999</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>26.75</v>
+        <v>25.5</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>22.95</v>
+        <v>24.4</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>23.65</v>
+        <v>24.9</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>157.67500000000001</v>
+        <v>164.02500000000001</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -1906,48 +2007,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24.175000000000001</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>26.824999999999999</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>23.024999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22.05</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>148.17500000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.71687499999999993</v>
+        <v>0.87562499999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.60437499999999988</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.71687499999999993</v>
+        <v>0.27125000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -21389,46 +21490,77 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>590</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>11</v>
+      </c>
+      <c r="G8" s="11">
+        <v>310</v>
+      </c>
+      <c r="H8" s="11">
+        <v>339</v>
+      </c>
+      <c r="I8" s="11">
+        <v>370</v>
+      </c>
       <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>42</v>
+      </c>
+      <c r="K8" s="12">
+        <v>24</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>590</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>11</v>
+      </c>
+      <c r="S8" s="11">
+        <v>295</v>
+      </c>
+      <c r="T8" s="11">
+        <v>320</v>
+      </c>
+      <c r="U8" s="11">
+        <v>345</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>39.024999999999999</v>
+      </c>
+      <c r="W8" s="12">
+        <v>24</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>39.024999999999999</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>2.9750000000000014</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -21437,41 +21569,69 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>73</v>
+      </c>
+      <c r="E9" s="11">
+        <v>56</v>
+      </c>
+      <c r="F9" s="11">
+        <v>79</v>
+      </c>
+      <c r="G9" s="11">
+        <v>82</v>
+      </c>
+      <c r="H9" s="11">
+        <v>78</v>
+      </c>
+      <c r="I9" s="11">
+        <v>88</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>11.4</v>
+      </c>
+      <c r="K9" s="12">
+        <v>13</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>56</v>
+      </c>
+      <c r="R9" s="11">
+        <v>79</v>
+      </c>
+      <c r="S9" s="11">
+        <v>82</v>
+      </c>
+      <c r="T9" s="11">
+        <v>78</v>
+      </c>
+      <c r="U9" s="11">
+        <v>88</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>11.4</v>
+      </c>
+      <c r="W9" s="12">
+        <v>13</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
@@ -21491,38 +21651,55 @@
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="K10" s="12">
+        <v>14</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>180</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>128</v>
+      </c>
+      <c r="T10" s="11">
+        <v>79</v>
+      </c>
+      <c r="U10" s="11">
+        <v>122</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>12.725</v>
+      </c>
+      <c r="W10" s="12">
+        <v>10</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12.725</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-0.72499999999999964</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -21530,46 +21707,78 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>196</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>95</v>
+      </c>
+      <c r="H11" s="11">
+        <v>90</v>
+      </c>
+      <c r="I11" s="11">
+        <v>95</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>11.9</v>
+      </c>
+      <c r="K11" s="12">
+        <v>4</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>201</v>
+      </c>
+      <c r="P11" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>5</v>
+      </c>
+      <c r="R11" s="11">
+        <v>5</v>
+      </c>
+      <c r="S11" s="11">
+        <v>100</v>
+      </c>
+      <c r="T11" s="11">
+        <v>95</v>
+      </c>
+      <c r="U11" s="11">
+        <v>100</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>12.775</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12.775</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-0.875</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -21577,46 +21786,78 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>90</v>
+      </c>
+      <c r="D12" s="11">
+        <v>18</v>
+      </c>
+      <c r="E12" s="11">
+        <v>16</v>
+      </c>
+      <c r="F12" s="11">
+        <v>12</v>
+      </c>
+      <c r="G12" s="11">
+        <v>24</v>
+      </c>
+      <c r="H12" s="11">
+        <v>17</v>
+      </c>
+      <c r="I12" s="11">
+        <v>10</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>4.6749999999999998</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>32</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>10</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>10</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>0</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>1.3</v>
+      </c>
+      <c r="W12" s="12">
+        <v>2</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.6749999999999998</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.375</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -21641,18 +21882,32 @@
       <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
+      <c r="O13" s="11">
+        <v>280</v>
+      </c>
+      <c r="P13" s="11">
+        <v>360</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>360</v>
+      </c>
+      <c r="R13" s="11">
+        <v>400</v>
+      </c>
+      <c r="S13" s="11">
+        <v>360</v>
+      </c>
+      <c r="T13" s="11">
+        <v>320</v>
+      </c>
       <c r="U13" s="11"/>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="W13" s="12">
+        <v>3</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -21812,83 +22067,83 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>563</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>2739</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>1283</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>892</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>655</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>5169</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>81.975000000000009</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>77.224999999999994</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>4.7500000000000018</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21897,36 +22152,36 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <f t="shared" ref="C19:I19" si="7">C18/40</f>
+        <v>21.9</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.2749999999999999</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.775</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.074999999999999</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>SUM(J8:J16)</f>
+        <v>81.975000000000009</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -21935,48 +22190,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>32.075000000000003</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10.775</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12.375</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24.375</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.375</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>129.22499999999999</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>2.0493750000000004</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.9306249999999998</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>0.11875000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -24342,29 +24597,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>84</v>
+      </c>
+      <c r="P8" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>25</v>
+      </c>
+      <c r="T8" s="11">
+        <v>45</v>
+      </c>
+      <c r="U8" s="11">
+        <v>50</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>6.1</v>
+      </c>
+      <c r="W8" s="12">
+        <v>12</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -24389,29 +24660,43 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
+      <c r="O9" s="11">
+        <v>80</v>
+      </c>
+      <c r="P9" s="11">
+        <v>105</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>99</v>
+      </c>
+      <c r="R9" s="11">
+        <v>115</v>
+      </c>
+      <c r="S9" s="11">
+        <v>54</v>
+      </c>
+      <c r="T9" s="11">
+        <v>55</v>
+      </c>
       <c r="U9" s="11"/>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>12.7</v>
+      </c>
+      <c r="W9" s="12">
+        <v>20</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="1">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="2">V9</f>
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="3">Y9-Z9</f>
-        <v>0</v>
+        <v>-12.7</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -24436,29 +24721,45 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>138</v>
+      </c>
+      <c r="P10" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>40</v>
+      </c>
+      <c r="R10" s="11">
+        <v>40</v>
+      </c>
+      <c r="S10" s="11">
+        <v>55</v>
+      </c>
+      <c r="T10" s="11">
+        <v>50</v>
+      </c>
+      <c r="U10" s="11">
+        <v>55</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>10.45</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.45</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10.45</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -24483,29 +24784,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>76</v>
+      </c>
+      <c r="P11" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="11">
+        <v>22</v>
+      </c>
+      <c r="S11" s="11">
+        <v>18</v>
+      </c>
+      <c r="T11" s="11">
+        <v>10</v>
+      </c>
+      <c r="U11" s="11">
+        <v>0</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>3.65</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -24530,29 +24847,45 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>128</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>12</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>12</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>3.8</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -24578,17 +24911,29 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
+      <c r="P13" s="11">
+        <v>160</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>160</v>
+      </c>
+      <c r="R13" s="11">
+        <v>200</v>
+      </c>
+      <c r="S13" s="11">
+        <v>360</v>
+      </c>
+      <c r="T13" s="11">
+        <v>280</v>
+      </c>
       <c r="U13" s="11"/>
       <c r="V13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -24783,35 +25128,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>2628</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -24820,11 +25165,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>36.699999999999996</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>-36.699999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24871,35 +25216,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>12.65</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.875</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.0250000000000004</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.4250000000000007</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.9249999999999998</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>65.7</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -24908,11 +25253,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.91749999999999987</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>-0.91749999999999987</v>
       </c>
     </row>
   </sheetData>
@@ -25417,30 +25762,15 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11">
-        <v>120</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>120</v>
-      </c>
-      <c r="R12" s="11">
-        <f>120+120</f>
-        <v>240</v>
-      </c>
-      <c r="S12" s="11">
-        <v>200</v>
-      </c>
-      <c r="T12" s="11">
-        <f>40+200</f>
-        <v>240</v>
-      </c>
-      <c r="U12" s="11">
-        <f>40+200</f>
-        <v>240</v>
-      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
@@ -25449,11 +25779,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -25690,31 +26020,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1160</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -25723,11 +26053,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25779,31 +26109,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -25812,11 +26142,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.72499999999999998</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-0.72499999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
@@ -26325,30 +26655,16 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>280</v>
-      </c>
-      <c r="P12" s="11">
-        <v>638</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>480</v>
-      </c>
-      <c r="R12" s="11">
-        <v>679</v>
-      </c>
-      <c r="S12" s="11">
-        <v>760</v>
-      </c>
-      <c r="T12" s="11">
-        <v>640</v>
-      </c>
-      <c r="U12" s="11">
-        <v>1078</v>
-      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="70">
         <f t="shared" si="1"/>
-        <v>113.875</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
@@ -26357,11 +26673,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>113.875</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-113.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -26607,35 +26923,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>1880</v>
+        <v>1600</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>1360</v>
+        <v>600</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>1440</v>
+        <v>800</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>2078</v>
+        <v>1000</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>8555</v>
+        <v>4000</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -26644,11 +26960,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>213.875</v>
+        <v>100</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-213.875</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26695,35 +27011,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>15.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>16.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>51.95</v>
+        <v>25</v>
       </c>
       <c r="V19" s="69">
         <f t="shared" si="8"/>
-        <v>213.875</v>
+        <v>100</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -26732,11 +27048,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>5.3468749999999998</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-5.3468749999999998</v>
+        <v>-2.5</v>
       </c>
     </row>
   </sheetData>
